--- a/outputs/01a02455-4428-7e10-b65c-4328cbb55411/notas_metodos_III_2026.xlsx
+++ b/outputs/01a02455-4428-7e10-b65c-4328cbb55411/notas_metodos_III_2026.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="1" r:id="R673e02ee60be4a32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubrica" sheetId="2" r:id="R4aa0e696380949ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referência" sheetId="3" r:id="R1335dcc847b24f07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proveniência" sheetId="4" r:id="R63685f4cd1304659"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="1" r:id="R4fc297dc64e04e1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubrica" sheetId="2" r:id="R8b6183d8e77640b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referência" sheetId="3" r:id="R3799e2e60e634afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proveniência" sheetId="4" r:id="R872fdadac1854fda"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -687,34 +687,34 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
       <x:c r="H2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
       <x:c r="I2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
       <x:c r="J2" s="7" t="str">
-        <x:v>Notas locais para revisão docente. Nenhuma nota ou feedback foi lançado no Moodle; a planilha não calcula a média final da disciplina.</x:v>
+        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
@@ -767,7 +767,7 @@
       <x:c r="F5" s="23"/>
       <x:c r="G5" s="24" t="n">
         <x:f>AVERAGEIF(H8:H81,"&lt;&gt;Sem envio localizado",G8:G81)</x:f>
-        <x:v>8.442105263157895</x:v>
+        <x:v>8.456140350877192</x:v>
       </x:c>
       <x:c r="H5" s="25"/>
       <x:c r="I5" s="22" t="str">
@@ -995,7 +995,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G13" s="52" t="n">
-        <x:v>8.8</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="H13" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -1004,7 +1004,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J13" s="56" t="str">
-        <x:v>Cobertura completa e segundo teste correto; há pequenas inconsistências de denominador/limpeza na experiência administrativa.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 8,3. O trabalho identifica corretamente comparação e unidade, informa 1.038 × 26 e inspeciona categorias inválidas. A validação trata "NA" como categoria; depois corrige exp_adm e exp_car, mas não os 95 códigos de instr nem verifica os 17 ausentes de car_pub. A tabela recupera MAPA 482/524 e MinC 312/354, com intervalos de Wilson, mas a narrativa informa 88,03% e limites diferentes. O primeiro teste usa incorretamente 309/351 no MinC, contradizendo a tabela; p = 0,0519 ainda leva à não rejeição a 5%. A recodificação de alto_nivel e o teste 2 estão corretos: 187/525, 155/365 e p = 0,0389. As decisões a 10% e 1% também estão corretas. A questão amostral acerta a direção, mas não mostra 1/√2 e chama 1.025 de dobro de 525. O código não é autocontido: dados2 e exp_admin não são definidos e o caminho é local absoluto.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="40" customHeight="1">
@@ -1127,7 +1127,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G17" s="52" t="n">
-        <x:v>6.5</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="H17" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J17" s="56" t="str">
-        <x:v>O primeiro teste produz p-valor 0,0014 e há contradição entre o p-valor e a decisão; o segundo teste e a análise de tamanho amostral estão corretos.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 6,3. O relatório identifica corretamente artigo, MAPA/MinC e unidade, e documenta 1.038 × 26. A validação confunde NA textual com NA real: informa exp_adm = 0, exp_car = 1 e instr = 0, omite car_pub e não corrige adequadamente os códigos  1  e 3. A descritiva de exp_adm usa MAPA 482/525, em vez de 482/524, e MinC 309/365, em vez de 312/354. O primeiro teste estima 7,15 pontos percentuais e p = 0,0014; além do cálculo contaminado, afirma que 0,0014 é maior que 0,05 e decide não rejeitar, uma contradição central. Em contraste, alto_nivel é construído corretamente: 187/525 no MAPA, 155/365 no MinC, diferença de −6,85 pontos percentuais e p = 0,0395, com decisão correta a 5%; somente a conclusão final inverte a direção ao dizer que o MAPA tem proporção maior. A discussão dos níveis é correta para o teste 2, mas contraditória no teste 1. A seção de amostra duplicada acerta a divisão por √2 e a redução de 29,3%. O relatório é legível, numerado e inclui código e fonte.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="40" customHeight="1">
@@ -1400,7 +1400,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J25" s="56" t="str">
-        <x:v>Trabalho completo, correto, claro e reprodutível, com resultados alinhados ao gabarito.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 9,8. O relatório identifica a base com 1.038 linhas e 26 variáveis, verifica dados ausentes e códigos anômalos e reproduz corretamente os resultados centrais. Para experiência administrativa, encontra 482 casos entre 524 observações válidas no MAPA e 312 entre 354 no MinC. O primeiro teste produz p = 0,05716: não se rejeita a hipótese de igualdade a 5% ou 1%, mas ela é rejeitada a 10%. Para cargos de alto nível, encontra 187 entre 525 no MAPA e 155 entre 365 no MinC, com p = 0,03889, decisão correta a 5%. Também explica corretamente que dobrar a amostra reduz o erro-padrão por 1/√2, cerca de 29,3%. Os pequenos descontos decorrem de não fornecer a referência bibliográfica completa, chamar a unidade de “indicação” em vez de nomeação/ocupação e não mostrar explicitamente o código de importação e carregamento de pacotes.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="40" customHeight="1">
@@ -1523,7 +1523,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G29" s="52" t="n">
-        <x:v>6.8</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="H29" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -1532,7 +1532,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J29" s="56" t="str">
-        <x:v>Usa o total da pasta em vez das observações válidas para exp_adm, obtendo 85,5% no MinC e um primeiro teste incorreto; segundo teste correto.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 6,5. O relatório identifica corretamente artigo, MAPA/MinC e a nomeação observada como unidade, registra 1.038 × 26 e lista as variáveis. A inspeção de ausências é parcialmente adequada: aparecem instr = 95, exp_adm = 11, nivel = 0, indicacao = 0 e car_pub = 17; exp_car surge fragmentada em 75 textos "NA" e um &lt;NA&gt;, sem consolidar 76. Após detectar códigos inválidos de exp_adm, não os retira dos denominadores. A tabela usa n = 525/365, em vez de 524/354. Embora x = 482/312 esteja correto, proporções e intervalos ficam errados, sobretudo no MinC. O teste 1 passa a ter diferença de 6,33 pontos percentuais e p = 0,00275, em vez de aproximadamente 3,85 e p = 0,057; a rejeição a 5% é incorreta. Também faltam H0/H1, comando do teste e interpretação probabilística do p-valor. O segundo teste está essencialmente correto: 187/525, 155/365 e p = 0,0389. A discussão de 1% mistura 1% com 0,1% e apresenta desigualdade incoerente. Ao dobrar n, acerta a direção, mas não fornece EP/√2 nem a redução de 29,3%. O relatório é legível e indica a fonte, porém não exibe código suficiente para reprodução plena.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="40" customHeight="1">
@@ -1565,7 +1565,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J30" s="56" t="str">
-        <x:v>Trabalho completo, correto, claro e reprodutível, com resultados alinhados ao gabarito.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 9,8. O relatório identifica corretamente artigo, pastas e unidade de análise, além de registrar as 1.038 linhas e 26 colunas. Informa corretamente os ausentes em instr, exp_adm, exp_car, nivel e indicacao, mas não menciona os 17 ausentes de car_pub. As proporções de experiência administrativa e os intervalos coincidem com as referências: 482/524 no MAPA e 312/354 no MinC. O primeiro teste reporta p = 0,05716 e toma decisões corretas a 1%, 5% e 10%. A construção de alto_nivel, as proporções 187/525 e 155/365 e o segundo teste (p = 0,03889) também estão corretos. A explicação sobre dobrar a amostra usa corretamente 1/√2. Os descontos decorrem da omissão de car_pub, numeração duplicada de tabelas e alguns símbolos matemáticos mal renderizados.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="40" customHeight="1">
@@ -1820,7 +1820,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G38" s="52" t="n">
-        <x:v>6.6</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="H38" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -1829,7 +1829,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J38" s="56" t="str">
-        <x:v>Primeiro teste incorreto (p-valor 0,001241) por recodificação/argumentos inadequados; segundo teste correto, mas a seção de significância mistura os testes.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 5,9. O relatório identifica adequadamente artigo, MAPA, MinC e a unidade de análise e informa corretamente 1.038 linhas e 26 colunas. A validação, porém, confunde textos "NA" com ausências reais: declara exp_adm = 0, instr = 0 e exp_car = 1, quando os totais são 11, 95 e 76, e não verifica car_pub. A recodificação deixa de reconhecer três ocorrências de  1 . A descritiva usa n() como denominador bruto e apresenta MAPA n = 525, x = 482 e MinC n = 365, x = 309, em vez de 524/482 e 354/312. Também faltam os intervalos de confiança. No primeiro teste, a tabela mostra 0,8803 para o MinC, mas prop.test usa 309/365 = 0,8466, produzindo p = 0,001241 em vez de aproximadamente 0,057; as rejeições a 5% e 1% ficam erradas. Em contraste, alto_nivel é construído corretamente, com 187/525 e 155/365, e o segundo teste (p = 0,04601) é bem interpretado. A discussão de amostra maior acerta a direção do erro-padrão, mas omite 1/√2 e a redução de 29,3%.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="40" customHeight="1">
@@ -2117,7 +2117,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G47" s="52" t="n">
-        <x:v>4.7</x:v>
+        <x:v>5.4</x:v>
       </x:c>
       <x:c r="H47" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -2126,7 +2126,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J47" s="56" t="str">
-        <x:v>Validação incompleta, prosa contraditória no primeiro teste, ausência do segundo teste e falta do arquivo-fonte; acerta parte descritiva e a direção do efeito amostral.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 5,4. O relatório identifica corretamente artigo, pastas e unidade de análise e explica por que a mesma pessoa pode aparecer mais de uma vez. Registra 1.038 linhas, 26 colunas, variáveis e observações por órgão. Contudo, a estudante declara não ter conseguido calcular os valores ausentes, componente central da validação. Há tratamento parcial de código inválido, convertendo exp_adm = 3 em ausente. Na descritiva, a tabela apresenta corretamente MAPA n = 524, x = 482, p = 0,920 e MinC n = 354, x = 312, p = 0,881, além de intervalos aproximadamente corretos. A narrativa, porém, troca essas proporções por 91,5% e 85,5%, inconsistentes com a própria tabela. No primeiro teste, p = 0,05716, a direção e a rejeição a 10% estão corretos, mas o texto contraditoriamente afirma rejeição a 5%; a decisão a 1% fica incompleta. Não há construção de alto_nivel nem segundo teste. Sobre ampliar a amostra, reconhece a redução do erro-padrão, mas não apresenta 1/√2 e afirma proporcionalidade inversa direta a n. O código é fragmentário.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="40" customHeight="1">
@@ -2216,7 +2216,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G50" s="52" t="n">
-        <x:v>8.8</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="H50" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -2225,7 +2225,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J50" s="56" t="str">
-        <x:v>Boa análise com testes corretos; pequenas inconsistências de validação, denominadores e apresentação.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 9,4. A identificação do artigo, das pastas e da unidade de análise está correta. A leitura informa 1.038 linhas, 26 colunas, variáveis e os principais ausentes, incluindo exp_adm = 11, exp_car = 76, instr = 95 e car_pub = 17. Há tratamento de códigos problemáticos, mas não se registram expressamente nivel = 0 e indicacao = 0, e converter exp_car = 5 para 3 é parcialmente conjectural. Para exp_adm, os resultados estão corretos: MAPA 482/524 e MinC 312/354. Os intervalos de Wald são coerentes, mas a descrição como “95% de certeza” e “5% de erro” é imprecisa. O primeiro teste preserva o estimando, obtém diferença −0,03849 e p = 0,0573. alto_nivel, as proporções 35,62% e 42,47%, a diferença 0,06847 e p = 0,0389 também estão corretos, embora “comprovar” seja excessivo e a segunda tabela não apareça. As decisões a 10% e 1% são corretas, mas não rejeitar não permite afirmar igualdade. A redução do erro-padrão por 1/√2, de 0,02022 para 0,01429, está correta.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="40" customHeight="1">
@@ -2315,7 +2315,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G53" s="52" t="n">
-        <x:v>6.2</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="H53" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -2324,7 +2324,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J53" s="56" t="str">
-        <x:v>Usa t.test e dados recodificados incorretamente no primeiro teste e produz tabela/teste de alto nível incorretos; acerta a lógica dos níveis de significância e o efeito amostral.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 8,3. O relatório identifica artigo e pastas e explica por que uma pessoa pode reaparecer, mas descreve a unidade como “pessoas nomeadas”, sem definir com precisão que cada linha representa um ocupante/cargo observado. Informa corretamente 1.038 linhas, 26 colunas, nomes das variáveis e ausências em sete campos. Inspeciona valores de exp_adm, exp_car, nivel, instr e indicacao; contudo, a limpeza de exp_adm produz erro no MinC: n = 351 e x = 309, em vez de n = 354 e x = 312. MAPA está correto: 524, 482 e 91,98%; ambos os intervalos são informados. No teste 1, o uso de teste t sobre variável binária preserva aproximadamente o estimando e gera p = 0,0607, dentro da faixa defensável; a decisão a 5% está correta, embora a explicação do p-valor confunda riscos de erro. O segundo teste é bem executado: construção de alto_nivel, contagens exatas e p = 0,0388873, mas falta avaliar substantivamente a magnitude. As decisões a 10% e 1% estão corretas, apesar de chamar 0,0607 de alfa. Reconhece que dobrar n reduz o erro-padrão, mas omite 1/√2. Os resultados são legíveis, porém não aparece o código gerador.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="40" customHeight="1">
@@ -2414,7 +2414,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G56" s="52" t="n">
-        <x:v>8.8</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="H56" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -2423,7 +2423,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J56" s="56" t="str">
-        <x:v>Testes centrais corretos; pequenas inconsistências na tabela descritiva, validação e apresentação.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 7,7. O relatório acerta a identificação do artigo, das pastas e da nomeação como unidade de análise. Informa corretamente 1.038 linhas, 26 colunas e frequências por órgão. A validação, porém, é internamente inconsistente: a Tabela 3 registra zero ausentes em instr e exp_adm e somente um em exp_car, enquanto o texto posterior encontra corretamente 95, 11 e 76. A limpeza exclui códigos tipográficos de exp_adm que deveriam ser normalizados, reduzindo indevidamente o MinC a 351 observações e 309 sucessos, em vez de 354 e 312. Isso afeta a descritiva e o primeiro teste, embora proporções, intervalos e p = 0,05187 permaneçam próximos e a decisão a 5% seja correta. Para alto_nivel, construção, contagens, proporções e p = 0,03889 estão corretos; contudo, o texto primeiro rejeita H0 e logo depois afirma o oposto, uma contradição decisória importante, e não julga claramente a magnitude substantiva. As decisões a 10% e 1% estão corretas. Ao dobrar a amostra, demonstra uma redução aproximadamente compatível com 1/√2, mas não explicita esse fator. O PDF documenta scripts, fonte e execução, embora contenha repetições e contradições.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="40" customHeight="1">
@@ -2494,7 +2494,7 @@
     </x:row>
     <x:row r="59" ht="40" customHeight="1">
       <x:c r="A59" s="46" t="str">
-        <x:v>Mariana Araujo Puschel</x:v>
+        <x:v>Mariana Araujo Püschel</x:v>
       </x:c>
       <x:c r="B59" s="48" t="str">
         <x:v>4725594</x:v>
@@ -2513,7 +2513,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G59" s="52" t="n">
-        <x:v>4.5</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H59" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -2522,7 +2522,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J59" s="56" t="str">
-        <x:v>Altera o estimando ao combinar exp_adm e exp_car, usa exp_car em vez de nivel no segundo teste, inverte decisões de significância e simula a duplicação de n incorretamente.</x:v>
+        <x:v>Nota final ajustada pelo docente para 5,0 (releitura independente: 4,2). Há acertos na identificação do estudo e da unidade: nomeações em MAPA e MinC, com possível repetição do indivíduo. A leitura registra 1.038 linhas, 26 colunas, variáveis e vários totais de ausências, além de códigos inesperados em exp_adm. Contudo, não trata esses códigos adequadamente e confunde as escalas de exp_car e nivel. Na descritiva, combina exp_adm e exp_car e converte ausências ou erros em ausência de experiência, produzindo MinC 309/365 = 0,8466, em vez de 312/354 = 0,8814, e MAPA 483/525 com denominador incorreto. O teste 1 retorna p = 0,000569 e rejeita a 5%, quando o teste correto tem p ≈ 0,057 e não rejeita a 5%. No segundo bloco, alto_nivel é derivada de exp_car, não de nivel = 5/6, alterando proporções, direção e p-valor: 0,3987, em vez de aproximadamente 0,0389. As decisões a 10% e 1% ficam erradas e a discussão inverte a exigência dos limiares. A apresentação é organizada, mas falta código reprodutível das recodificações-chave. Ao dobrar n, mantém os sucessos fixos e não demonstra a redução por 1/√2.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="40" customHeight="1">
@@ -2546,7 +2546,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G60" s="52" t="n">
-        <x:v>5.8</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="H60" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -2555,7 +2555,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J60" s="56" t="str">
-        <x:v>Primeiro teste incorreto (p-valor 0,000844) e respostas condicionais sem concluir os testes; segundo teste e significância ficam incompletos, embora haja boa estrutura.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 6,3. O relatório identifica adequadamente artigo, ministérios e unidade de análise, informa 1.038 × 26 e lista as variáveis. O problema central é a limpeza: colSums(is.na()) contabiliza somente ausências lógicas e retorna 0/1/0 para exp_adm/exp_car/instr, embora as tabelas exibam códigos textuais ou inválidos; car_pub não é verificada. O texto afirma que recodificaria os valores, mas o código não executa essa etapa. Isso contamina as questões 3 e 4: usa MAPA n = 525, x = 482, p = 0,9181 e MinC n = 365, x = 309, p = 0,8466, em vez de n = 524/354, x = 482/312 e p ≈ 0,9199/0,8814. O teste 1 produz p = 0,000845, incompatível com a referência p ≈ 0,057, que implica rejeição somente a 10%. Em contraste, alto_nivel é construído corretamente; as proporções 0,3562 e 0,4247 e p = 0,03889 sustentam rejeição a 5%, mas não a 1%. A discussão de alfa é conceitualmente correta, porém não decide explicitamente os dois testes. A questão sobre amostra maior acerta direção e estreitamento do intervalo, mas omite 1/√2 e a redução de 29,3%. Código e saídas são legíveis, embora a limpeza anunciada não seja executada.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="40" customHeight="1">
@@ -2678,7 +2678,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G64" s="52" t="n">
-        <x:v>9.8</x:v>
+        <x:v>9.2</x:v>
       </x:c>
       <x:c r="H64" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -2687,7 +2687,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J64" s="56" t="str">
-        <x:v>Trabalho completo, correto, claro e reprodutível, com resultados alinhados ao gabarito.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 9,2. O relatório identifica artigo, pastas e unidade, e recupera 1.038 × 26. O principal desconto está na validação: is.na() leva o texto a informar instr = 0, exp_adm = 0 e exp_car = 1, embora existam códigos textuais "NA": 95 em instr, 75 em exp_car, além de um ausente real, e 11 ausentes reais em exp_adm; somente exp_adm é explicitamente corrigida. As contagens e proporções são corretas: MAPA 482/524 e MinC 312/354. Os intervalos na tabela estão corretos, mas a narrativa apresenta valores diferentes. O teste 1 (p = 0,05716), as decisões por nível de significância, a construção de alto_nivel, o teste 2 (p = 0,03889) e a razão 0,7071 para o erro-padrão estão corretos. Não aparecem os comandos de carregamento dos pacotes.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="40" customHeight="1">
@@ -2711,7 +2711,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G65" s="52" t="n">
-        <x:v>6.1</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="H65" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -2720,7 +2720,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J65" s="56" t="str">
-        <x:v>Tratamento da base altera as contagens (312/355 e 152 altos no MinC), gerando p-valor 0,103 e conclusão incorreta também para alto nível; apresentação é extensa e cuidadosa.</x:v>
+        <x:v>Nota adotada após releitura independente cega: 5,9. O relatório acerta a pergunta do artigo, a comparação e a unidade como evento de nomeação. Mostra 1.038 × 26, mas não apresenta a lista efetiva de variáveis nem as contagens de ausentes; descreve validação sem exibir resultados e usa limpeza/complete.cases que altera indevidamente as amostras. Em exp_adm, MAPA está correto: 482/524 = 0,9198; MinC aparece como 315/355 = 0,8873, em vez de 312/354 = 0,8814. O teste 1 produz p = 0,1038, fora da faixa aceitável de aproximadamente 0,052–0,074, e deixa de rejeitar a 10%. A recodificação alto_nivel = 1 para níveis 5–6 é correta; MAPA fica próximo do gabarito, mas MinC usa 152/355, em vez de 155/365. O relatório não executa o segundo teste: reutiliza p = 0,1038 de exp_adm para discutir alto_nivel, gerando conclusão errada diante de p ≈ 0,0389. A explicação sobre dobrar n é excelente: o erro-padrão cai por 1/√2, cerca de 29%. Há código, fonte, tabelas e gráficos legíveis, mas a cadeia contém uma inconsistência inferencial grave.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="40" customHeight="1">
@@ -3284,7 +3284,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e62381d00fc4434"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R004765caeae84fa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3844,99 +3844,127 @@
     </x:row>
     <x:row r="10" ht="65" customHeight="1">
       <x:c r="A10" s="46" t="str">
-        <x:v>OCR das submissões</x:v>
+        <x:v>Loop independente</x:v>
       </x:c>
       <x:c r="B10" s="56" t="str">
-        <x:v>/Users/manoelgaldino/Documents/DCP/Papers/metodos_CP/tmp/grading_work/moodle_ocr/manifest.json</x:v>
+        <x:v>/Users/manoelgaldino/Documents/DCP/Papers/metodos_CP/tmp/grading_work/independent_review_results.csv</x:v>
       </x:c>
       <x:c r="C10" s="56" t="str">
-        <x:v>1.818 capturas processadas; 56 estudantes; 0 falhas de OCR.</x:v>
+        <x:v>14 releituras cegas; notas do loop adotadas nos casos selecionados.</x:v>
       </x:c>
       <x:c r="D10" s="56" t="str">
-        <x:v>0d2f582d0d530d2df8d573009d5e93a549e260ccd551a016e4b90d78e5842379</x:v>
+        <x:v>Resultados brutos preservados</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="65" customHeight="1">
       <x:c r="A11" s="46" t="str">
-        <x:v>Enunciado</x:v>
+        <x:v>Ajuste docente</x:v>
       </x:c>
       <x:c r="B11" s="56" t="str">
-        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/avaliacao_aulas_06_09_inferencia_basica.Rmd</x:v>
+        <x:v>Mariana Araujo Püschel — NUSP 4725594</x:v>
       </x:c>
       <x:c r="C11" s="56" t="str">
-        <x:v>Instruções exatas do trabalho final recuperadas no repositório da disciplina.</x:v>
+        <x:v>Nota do loop: 4,2; nota final adotada: 5,0 por decisão do docente.</x:v>
       </x:c>
       <x:c r="D11" s="56" t="str">
-        <x:v>838c72cc19a6e6beef81954e5109291d285fd570c2cbeb5e211720520836f616</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="65" customHeight="1">
       <x:c r="A12" s="46" t="str">
-        <x:v>Gabarito</x:v>
+        <x:v>OCR das submissões</x:v>
       </x:c>
       <x:c r="B12" s="56" t="str">
-        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/avaliacao_aulas_06_09_gabarito.Rmd</x:v>
+        <x:v>/Users/manoelgaldino/Documents/DCP/Papers/metodos_CP/tmp/grading_work/moodle_ocr/manifest.json</x:v>
       </x:c>
       <x:c r="C12" s="56" t="str">
-        <x:v>Âncoras substantivas e decisões estatísticas usadas na rubrica.</x:v>
+        <x:v>1.818 capturas processadas; 56 estudantes; 0 falhas de OCR.</x:v>
       </x:c>
       <x:c r="D12" s="56" t="str">
-        <x:v>a02f205062dcc2684456209232785b37a243c91959cc25b1a1f018bc37177b81</x:v>
+        <x:v>0d2f582d0d530d2df8d573009d5e93a549e260ccd551a016e4b90d78e5842379</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="65" customHeight="1">
       <x:c r="A13" s="46" t="str">
-        <x:v>Cálculos do gabarito</x:v>
+        <x:v>Enunciado</x:v>
       </x:c>
       <x:c r="B13" s="56" t="str">
-        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/scripts/avaliacao_aulas_06_09_gabarito_calculos.R</x:v>
+        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/avaliacao_aulas_06_09_inferencia_basica.Rmd</x:v>
       </x:c>
       <x:c r="C13" s="56" t="str">
-        <x:v>Script reprodutível dos valores de referência.</x:v>
+        <x:v>Instruções exatas do trabalho final recuperadas no repositório da disciplina.</x:v>
       </x:c>
       <x:c r="D13" s="56" t="str">
-        <x:v>a9f3ff20c646087ae38c62594c5c16600ed22995d93005825c0eea41f39fb9db</x:v>
+        <x:v>838c72cc19a6e6beef81954e5109291d285fd570c2cbeb5e211720520836f616</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="65" customHeight="1">
       <x:c r="A14" s="46" t="str">
-        <x:v>Estado externo</x:v>
+        <x:v>Gabarito</x:v>
       </x:c>
       <x:c r="B14" s="56" t="str">
-        <x:v>Moodle</x:v>
+        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/avaliacao_aulas_06_09_gabarito.Rmd</x:v>
       </x:c>
       <x:c r="C14" s="56" t="str">
-        <x:v>Nenhuma nota ou devolutiva foi lançada; acesso apenas para leitura/coleta.</x:v>
+        <x:v>Âncoras substantivas e decisões estatísticas usadas na rubrica.</x:v>
       </x:c>
       <x:c r="D14" s="56" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>a02f205062dcc2684456209232785b37a243c91959cc25b1a1f018bc37177b81</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="65" customHeight="1">
       <x:c r="A15" s="46" t="str">
-        <x:v>Escopo da nota</x:v>
+        <x:v>Cálculos do gabarito</x:v>
       </x:c>
       <x:c r="B15" s="56" t="str">
-        <x:v>Trabalho final</x:v>
+        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/scripts/avaliacao_aulas_06_09_gabarito_calculos.R</x:v>
       </x:c>
       <x:c r="C15" s="56" t="str">
-        <x:v>A planilha não calcula média final da disciplina; notas de listas são auxiliares.</x:v>
+        <x:v>Script reprodutível dos valores de referência.</x:v>
       </x:c>
       <x:c r="D15" s="56" t="str">
-        <x:v>Escala 0–10</x:v>
+        <x:v>a9f3ff20c646087ae38c62594c5c16600ed22995d93005825c0eea41f39fb9db</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="65" customHeight="1">
       <x:c r="A16" s="46" t="str">
+        <x:v>Estado externo</x:v>
+      </x:c>
+      <x:c r="B16" s="56" t="str">
+        <x:v>Moodle</x:v>
+      </x:c>
+      <x:c r="C16" s="56" t="str">
+        <x:v>Nenhuma nota ou devolutiva foi lançada; acesso apenas para leitura/coleta.</x:v>
+      </x:c>
+      <x:c r="D16" s="56" t="str">
+        <x:v>2026-08-21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="65" customHeight="1">
+      <x:c r="A17" s="46" t="str">
+        <x:v>Escopo da nota</x:v>
+      </x:c>
+      <x:c r="B17" s="56" t="str">
+        <x:v>Trabalho final</x:v>
+      </x:c>
+      <x:c r="C17" s="56" t="str">
+        <x:v>A planilha não calcula média final da disciplina; notas de listas são auxiliares.</x:v>
+      </x:c>
+      <x:c r="D17" s="56" t="str">
+        <x:v>Escala 0–10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="65" customHeight="1">
+      <x:c r="A18" s="46" t="str">
         <x:v>Caso de leitura longa</x:v>
       </x:c>
-      <x:c r="B16" s="56" t="str">
+      <x:c r="B18" s="56" t="str">
         <x:v>Agnes Francisca Carraro Kunsch — NUSP 14554690</x:v>
       </x:c>
-      <x:c r="C16" s="56" t="str">
+      <x:c r="C18" s="56" t="str">
         <x:v>PDF de 206 páginas: capa/análise e páginas finais foram verificadas; miolo era impressão da base.</x:v>
       </x:c>
-      <x:c r="D16" s="56" t="str">
+      <x:c r="D18" s="56" t="str">
         <x:v>Amostra: p. 1 e 197–206</x:v>
       </x:c>
     </x:row>

--- a/outputs/01a02455-4428-7e10-b65c-4328cbb55411/notas_metodos_III_2026.xlsx
+++ b/outputs/01a02455-4428-7e10-b65c-4328cbb55411/notas_metodos_III_2026.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="1" r:id="R4fc297dc64e04e1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubrica" sheetId="2" r:id="R8b6183d8e77640b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referência" sheetId="3" r:id="R3799e2e60e634afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proveniência" sheetId="4" r:id="R872fdadac1854fda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="1" r:id="Re4cf10c98b154241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubrica" sheetId="2" r:id="Ra6120d38e878440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referência" sheetId="3" r:id="R433ba5b2fdb6480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proveniência" sheetId="4" r:id="Ra5d94755d04d4e3c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -687,34 +687,34 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
       <x:c r="H2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
       <x:c r="I2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
       <x:c r="J2" s="7" t="str">
-        <x:v>Notas adotadas após releitura independente dos 14 trabalhos selecionados; Mariana Araujo Püschel ajustada para 5,0 por decisão docente. Nenhuma nota foi lançada no Moodle.</x:v>
+        <x:v>Notas adotadas após releitura independente; Mariana Araujo Püschel ajustada para 5,0 e descontos docentes de 1,5 ponto aplicados a duas suspeitas não comprovadas de assistência por IA. Nada foi lançado no Moodle.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
@@ -767,7 +767,7 @@
       <x:c r="F5" s="23"/>
       <x:c r="G5" s="24" t="n">
         <x:f>AVERAGEIF(H8:H81,"&lt;&gt;Sem envio localizado",G8:G81)</x:f>
-        <x:v>8.456140350877192</x:v>
+        <x:v>8.403508771929824</x:v>
       </x:c>
       <x:c r="H5" s="25"/>
       <x:c r="I5" s="22" t="str">
@@ -995,7 +995,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G13" s="52" t="n">
-        <x:v>8.3</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="H13" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -1004,7 +1004,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J13" s="56" t="str">
-        <x:v>Nota adotada após releitura independente cega: 8,3. O trabalho identifica corretamente comparação e unidade, informa 1.038 × 26 e inspeciona categorias inválidas. A validação trata "NA" como categoria; depois corrige exp_adm e exp_car, mas não os 95 códigos de instr nem verifica os 17 ausentes de car_pub. A tabela recupera MAPA 482/524 e MinC 312/354, com intervalos de Wilson, mas a narrativa informa 88,03% e limites diferentes. O primeiro teste usa incorretamente 309/351 no MinC, contradizendo a tabela; p = 0,0519 ainda leva à não rejeição a 5%. A recodificação de alto_nivel e o teste 2 estão corretos: 187/525, 155/365 e p = 0,0389. As decisões a 10% e 1% também estão corretas. A questão amostral acerta a direção, mas não mostra 1/√2 e chama 1.025 de dobro de 525. O código não é autocontido: dados2 e exp_admin não são definidos e o caminho é local absoluto.</x:v>
+        <x:v>Nota final 6,8 após desconto docente de 1,5 ponto por suspeita não comprovada de assistência por IA (releitura independente: 8,3). O trabalho identifica corretamente comparação e unidade, informa 1.038 × 26 e inspeciona categorias inválidas. A validação trata "NA" como categoria; depois corrige exp_adm e exp_car, mas não os 95 códigos de instr nem verifica os 17 ausentes de car_pub. A tabela recupera MAPA 482/524 e MinC 312/354, com intervalos de Wilson, mas a narrativa informa 88,03% e limites diferentes. O primeiro teste usa incorretamente 309/351 no MinC, contradizendo a tabela; p = 0,0519 ainda leva à não rejeição a 5%. A recodificação de alto_nivel e o teste 2 estão corretos: 187/525, 155/365 e p = 0,0389. As decisões a 10% e 1% também estão corretas. A questão amostral acerta a direção, mas não mostra 1/√2 e chama 1.025 de dobro de 525. O código não é autocontido: dados2 e exp_admin não são definidos e o caminho é local absoluto.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="40" customHeight="1">
@@ -1556,7 +1556,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G30" s="52" t="n">
-        <x:v>9.8</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="H30" s="54" t="str">
         <x:v>Entregue no Moodle</x:v>
@@ -1565,7 +1565,7 @@
         <x:v>Moodle</x:v>
       </x:c>
       <x:c r="J30" s="56" t="str">
-        <x:v>Nota adotada após releitura independente cega: 9,8. O relatório identifica corretamente artigo, pastas e unidade de análise, além de registrar as 1.038 linhas e 26 colunas. Informa corretamente os ausentes em instr, exp_adm, exp_car, nivel e indicacao, mas não menciona os 17 ausentes de car_pub. As proporções de experiência administrativa e os intervalos coincidem com as referências: 482/524 no MAPA e 312/354 no MinC. O primeiro teste reporta p = 0,05716 e toma decisões corretas a 1%, 5% e 10%. A construção de alto_nivel, as proporções 187/525 e 155/365 e o segundo teste (p = 0,03889) também estão corretos. A explicação sobre dobrar a amostra usa corretamente 1/√2. Os descontos decorrem da omissão de car_pub, numeração duplicada de tabelas e alguns símbolos matemáticos mal renderizados.</x:v>
+        <x:v>Nota final 8,3 após desconto docente de 1,5 ponto por suspeita não comprovada de assistência por IA (releitura independente: 9,8). O relatório identifica corretamente artigo, pastas e unidade de análise, além de registrar as 1.038 linhas e 26 colunas. Informa corretamente os ausentes em instr, exp_adm, exp_car, nivel e indicacao, mas não menciona os 17 ausentes de car_pub. As proporções de experiência administrativa e os intervalos coincidem com as referências: 482/524 no MAPA e 312/354 no MinC. O primeiro teste reporta p = 0,05716 e toma decisões corretas a 1%, 5% e 10%. A construção de alto_nivel, as proporções 187/525 e 155/365 e o segundo teste (p = 0,03889) também estão corretos. A explicação sobre dobrar a amostra usa corretamente 1/√2. Os descontos decorrem da omissão de car_pub, numeração duplicada de tabelas e alguns símbolos matemáticos mal renderizados.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="40" customHeight="1">
@@ -3284,7 +3284,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R004765caeae84fa6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0c82456b8ab427c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3872,99 +3872,113 @@
     </x:row>
     <x:row r="12" ht="65" customHeight="1">
       <x:c r="A12" s="46" t="str">
-        <x:v>OCR das submissões</x:v>
+        <x:v>Desconto por suspeita de IA</x:v>
       </x:c>
       <x:c r="B12" s="56" t="str">
-        <x:v>/Users/manoelgaldino/Documents/DCP/Papers/metodos_CP/tmp/grading_work/moodle_ocr/manifest.json</x:v>
+        <x:v>Gabriela Yumi Fraga Assano — NUSP 14573451; Beatriz Pessoni — NUSP 15442662</x:v>
       </x:c>
       <x:c r="C12" s="56" t="str">
-        <x:v>1.818 capturas processadas; 56 estudantes; 0 falhas de OCR.</x:v>
+        <x:v>Desconto docente de 1,5 ponto para cada aluna; notas finais 8,3 e 6,8. Suspeitas registradas como não comprovadas.</x:v>
       </x:c>
       <x:c r="D12" s="56" t="str">
-        <x:v>0d2f582d0d530d2df8d573009d5e93a549e260ccd551a016e4b90d78e5842379</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="65" customHeight="1">
       <x:c r="A13" s="46" t="str">
-        <x:v>Enunciado</x:v>
+        <x:v>OCR das submissões</x:v>
       </x:c>
       <x:c r="B13" s="56" t="str">
-        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/avaliacao_aulas_06_09_inferencia_basica.Rmd</x:v>
+        <x:v>/Users/manoelgaldino/Documents/DCP/Papers/metodos_CP/tmp/grading_work/moodle_ocr/manifest.json</x:v>
       </x:c>
       <x:c r="C13" s="56" t="str">
-        <x:v>Instruções exatas do trabalho final recuperadas no repositório da disciplina.</x:v>
+        <x:v>1.818 capturas processadas; 56 estudantes; 0 falhas de OCR.</x:v>
       </x:c>
       <x:c r="D13" s="56" t="str">
-        <x:v>838c72cc19a6e6beef81954e5109291d285fd570c2cbeb5e211720520836f616</x:v>
+        <x:v>0d2f582d0d530d2df8d573009d5e93a549e260ccd551a016e4b90d78e5842379</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="65" customHeight="1">
       <x:c r="A14" s="46" t="str">
-        <x:v>Gabarito</x:v>
+        <x:v>Enunciado</x:v>
       </x:c>
       <x:c r="B14" s="56" t="str">
-        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/avaliacao_aulas_06_09_gabarito.Rmd</x:v>
+        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/avaliacao_aulas_06_09_inferencia_basica.Rmd</x:v>
       </x:c>
       <x:c r="C14" s="56" t="str">
-        <x:v>Âncoras substantivas e decisões estatísticas usadas na rubrica.</x:v>
+        <x:v>Instruções exatas do trabalho final recuperadas no repositório da disciplina.</x:v>
       </x:c>
       <x:c r="D14" s="56" t="str">
-        <x:v>a02f205062dcc2684456209232785b37a243c91959cc25b1a1f018bc37177b81</x:v>
+        <x:v>838c72cc19a6e6beef81954e5109291d285fd570c2cbeb5e211720520836f616</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="65" customHeight="1">
       <x:c r="A15" s="46" t="str">
-        <x:v>Cálculos do gabarito</x:v>
+        <x:v>Gabarito</x:v>
       </x:c>
       <x:c r="B15" s="56" t="str">
-        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/scripts/avaliacao_aulas_06_09_gabarito_calculos.R</x:v>
+        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/avaliacao_aulas_06_09_gabarito.Rmd</x:v>
       </x:c>
       <x:c r="C15" s="56" t="str">
-        <x:v>Script reprodutível dos valores de referência.</x:v>
+        <x:v>Âncoras substantivas e decisões estatísticas usadas na rubrica.</x:v>
       </x:c>
       <x:c r="D15" s="56" t="str">
-        <x:v>a9f3ff20c646087ae38c62594c5c16600ed22995d93005825c0eea41f39fb9db</x:v>
+        <x:v>a02f205062dcc2684456209232785b37a243c91959cc25b1a1f018bc37177b81</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="65" customHeight="1">
       <x:c r="A16" s="46" t="str">
-        <x:v>Estado externo</x:v>
+        <x:v>Cálculos do gabarito</x:v>
       </x:c>
       <x:c r="B16" s="56" t="str">
-        <x:v>Moodle</x:v>
+        <x:v>/Users/manoelgaldino/Documents/DCP/Cursos/stat_basica/book-stat-basica/scripts/avaliacao_aulas_06_09_gabarito_calculos.R</x:v>
       </x:c>
       <x:c r="C16" s="56" t="str">
-        <x:v>Nenhuma nota ou devolutiva foi lançada; acesso apenas para leitura/coleta.</x:v>
+        <x:v>Script reprodutível dos valores de referência.</x:v>
       </x:c>
       <x:c r="D16" s="56" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>a9f3ff20c646087ae38c62594c5c16600ed22995d93005825c0eea41f39fb9db</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="65" customHeight="1">
       <x:c r="A17" s="46" t="str">
-        <x:v>Escopo da nota</x:v>
+        <x:v>Estado externo</x:v>
       </x:c>
       <x:c r="B17" s="56" t="str">
-        <x:v>Trabalho final</x:v>
+        <x:v>Moodle</x:v>
       </x:c>
       <x:c r="C17" s="56" t="str">
-        <x:v>A planilha não calcula média final da disciplina; notas de listas são auxiliares.</x:v>
+        <x:v>Nenhuma nota ou devolutiva foi lançada; acesso apenas para leitura/coleta.</x:v>
       </x:c>
       <x:c r="D17" s="56" t="str">
-        <x:v>Escala 0–10</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="65" customHeight="1">
       <x:c r="A18" s="46" t="str">
+        <x:v>Escopo da nota</x:v>
+      </x:c>
+      <x:c r="B18" s="56" t="str">
+        <x:v>Trabalho final</x:v>
+      </x:c>
+      <x:c r="C18" s="56" t="str">
+        <x:v>A planilha não calcula média final da disciplina; notas de listas são auxiliares.</x:v>
+      </x:c>
+      <x:c r="D18" s="56" t="str">
+        <x:v>Escala 0–10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="65" customHeight="1">
+      <x:c r="A19" s="46" t="str">
         <x:v>Caso de leitura longa</x:v>
       </x:c>
-      <x:c r="B18" s="56" t="str">
+      <x:c r="B19" s="56" t="str">
         <x:v>Agnes Francisca Carraro Kunsch — NUSP 14554690</x:v>
       </x:c>
-      <x:c r="C18" s="56" t="str">
+      <x:c r="C19" s="56" t="str">
         <x:v>PDF de 206 páginas: capa/análise e páginas finais foram verificadas; miolo era impressão da base.</x:v>
       </x:c>
-      <x:c r="D18" s="56" t="str">
+      <x:c r="D19" s="56" t="str">
         <x:v>Amostra: p. 1 e 197–206</x:v>
       </x:c>
     </x:row>
